--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/92.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/92.xlsx
@@ -426,13 +426,13 @@
         <v>-6.882248770942923</v>
       </c>
       <c r="E2">
-        <v>-16.23412854680507</v>
+        <v>-14.88270963411802</v>
       </c>
       <c r="F2">
-        <v>0.04659303405775604</v>
+        <v>0.001673983273550049</v>
       </c>
       <c r="G2">
-        <v>-14.41801128548203</v>
+        <v>-10.8800428545723</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.603433536808725</v>
       </c>
       <c r="E3">
-        <v>-16.71412414924809</v>
+        <v>-15.84590699860149</v>
       </c>
       <c r="F3">
-        <v>-0.07619255258960347</v>
+        <v>-0.112771600362424</v>
       </c>
       <c r="G3">
-        <v>-14.08796810321716</v>
+        <v>-11.18011401279738</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.316985689220451</v>
       </c>
       <c r="E4">
-        <v>-17.06532995091296</v>
+        <v>-16.1398049616993</v>
       </c>
       <c r="F4">
-        <v>0.25704557131079</v>
+        <v>0.218823870978218</v>
       </c>
       <c r="G4">
-        <v>-13.29535397965932</v>
+        <v>-10.39125404788107</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.037044293544216</v>
       </c>
       <c r="E5">
-        <v>-17.06003616479799</v>
+        <v>-16.40127905090219</v>
       </c>
       <c r="F5">
-        <v>0.6519349391645367</v>
+        <v>0.1877286154119302</v>
       </c>
       <c r="G5">
-        <v>-13.39342889126022</v>
+        <v>-11.25837199880022</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.744966906628862</v>
       </c>
       <c r="E6">
-        <v>-17.92992432235341</v>
+        <v>-17.23645645518882</v>
       </c>
       <c r="F6">
-        <v>0.7657368813285357</v>
+        <v>0.5100612824544682</v>
       </c>
       <c r="G6">
-        <v>-12.75908201829832</v>
+        <v>-10.37053996444185</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.441948930701612</v>
       </c>
       <c r="E7">
-        <v>-19.02332889997943</v>
+        <v>-17.56610219210317</v>
       </c>
       <c r="F7">
-        <v>0.8116648836093514</v>
+        <v>0.638431722131502</v>
       </c>
       <c r="G7">
-        <v>-12.29099405286414</v>
+        <v>-9.941867354198243</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.123577065032506</v>
       </c>
       <c r="E8">
-        <v>-18.84975701973944</v>
+        <v>-18.34415742525704</v>
       </c>
       <c r="F8">
-        <v>0.977948042577713</v>
+        <v>0.9663227344468247</v>
       </c>
       <c r="G8">
-        <v>-11.9090199979975</v>
+        <v>-9.650728047838117</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.786999754276556</v>
       </c>
       <c r="E9">
-        <v>-20.2444047453037</v>
+        <v>-19.56730278320282</v>
       </c>
       <c r="F9">
-        <v>1.154430061009342</v>
+        <v>1.10441986416753</v>
       </c>
       <c r="G9">
-        <v>-12.02608419881166</v>
+        <v>-9.862371224163724</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.431021707863183</v>
       </c>
       <c r="E10">
-        <v>-20.6135161331949</v>
+        <v>-19.50345129969466</v>
       </c>
       <c r="F10">
-        <v>1.440796672157131</v>
+        <v>1.031087811467301</v>
       </c>
       <c r="G10">
-        <v>-11.26307628401152</v>
+        <v>-9.072504853403473</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.062222955425689</v>
       </c>
       <c r="E11">
-        <v>-21.55889395245819</v>
+        <v>-20.07924676976995</v>
       </c>
       <c r="F11">
-        <v>1.539703740051392</v>
+        <v>1.4171451260724</v>
       </c>
       <c r="G11">
-        <v>-10.54566451292376</v>
+        <v>-8.739748679069168</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.683400007747991</v>
       </c>
       <c r="E12">
-        <v>-21.40081851027244</v>
+        <v>-20.36174656379045</v>
       </c>
       <c r="F12">
-        <v>1.979901491368661</v>
+        <v>1.687254198572846</v>
       </c>
       <c r="G12">
-        <v>-10.02278701881465</v>
+        <v>-7.811243282215318</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.297325099713147</v>
       </c>
       <c r="E13">
-        <v>-21.68146162994979</v>
+        <v>-21.5762561218036</v>
       </c>
       <c r="F13">
-        <v>1.943496400750428</v>
+        <v>1.871395302010759</v>
       </c>
       <c r="G13">
-        <v>-9.902660563376655</v>
+        <v>-7.963147664284776</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.919313951688025</v>
       </c>
       <c r="E14">
-        <v>-22.26344299551956</v>
+        <v>-22.01607057437656</v>
       </c>
       <c r="F14">
-        <v>1.847293124058905</v>
+        <v>1.921953878073224</v>
       </c>
       <c r="G14">
-        <v>-9.383871593008545</v>
+        <v>-6.649053096835392</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.560307064344006</v>
       </c>
       <c r="E15">
-        <v>-24.03101055561547</v>
+        <v>-22.68356311463316</v>
       </c>
       <c r="F15">
-        <v>2.394696527911679</v>
+        <v>2.365763311266698</v>
       </c>
       <c r="G15">
-        <v>-8.919282874209383</v>
+        <v>-7.23266916995351</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.229411026131739</v>
       </c>
       <c r="E16">
-        <v>-23.86987386500054</v>
+        <v>-23.08067405731379</v>
       </c>
       <c r="F16">
-        <v>2.305509523121868</v>
+        <v>2.43129048629775</v>
       </c>
       <c r="G16">
-        <v>-8.249595927615754</v>
+        <v>-6.023326884457745</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.938604370770465</v>
       </c>
       <c r="E17">
-        <v>-25.69547381950475</v>
+        <v>-24.57723056194666</v>
       </c>
       <c r="F17">
-        <v>2.833196126053209</v>
+        <v>2.607174423464558</v>
       </c>
       <c r="G17">
-        <v>-8.413176603802222</v>
+        <v>-5.802669092628703</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.692991437468207</v>
       </c>
       <c r="E18">
-        <v>-25.08034855267285</v>
+        <v>-25.31518162928861</v>
       </c>
       <c r="F18">
-        <v>2.282427893810262</v>
+        <v>3.503814210867993</v>
       </c>
       <c r="G18">
-        <v>-8.261854877747677</v>
+        <v>-5.029487871386378</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.488332831616119</v>
       </c>
       <c r="E19">
-        <v>-26.37578646967707</v>
+        <v>-26.04479577598244</v>
       </c>
       <c r="F19">
-        <v>2.94284711916178</v>
+        <v>3.072367332793899</v>
       </c>
       <c r="G19">
-        <v>-7.881069308729625</v>
+        <v>-4.595455487914689</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.316127441385741</v>
       </c>
       <c r="E20">
-        <v>-26.90474393309102</v>
+        <v>-26.76126376263199</v>
       </c>
       <c r="F20">
-        <v>3.305213126046812</v>
+        <v>3.35478428816514</v>
       </c>
       <c r="G20">
-        <v>-7.094712116241001</v>
+        <v>-4.978326700622481</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.16644463111162</v>
       </c>
       <c r="E21">
-        <v>-27.16084725212081</v>
+        <v>-27.07436245552232</v>
       </c>
       <c r="F21">
-        <v>3.082094022837571</v>
+        <v>3.523920344468743</v>
       </c>
       <c r="G21">
-        <v>-6.431659502908071</v>
+        <v>-5.062530426413844</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.0246032716781</v>
       </c>
       <c r="E22">
-        <v>-27.7835803552856</v>
+        <v>-27.84849150171155</v>
       </c>
       <c r="F22">
-        <v>3.308577954436984</v>
+        <v>3.583002821106015</v>
       </c>
       <c r="G22">
-        <v>-6.328473108994528</v>
+        <v>-4.488928753552021</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8765180222899338</v>
       </c>
       <c r="E23">
-        <v>-27.90813150439256</v>
+        <v>-27.83792657185165</v>
       </c>
       <c r="F23">
-        <v>3.258728460871315</v>
+        <v>3.304195890876174</v>
       </c>
       <c r="G23">
-        <v>-6.351418500127217</v>
+        <v>-3.725195829278777</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.7161880063690927</v>
       </c>
       <c r="E24">
-        <v>-28.8349380517504</v>
+        <v>-28.73946876272069</v>
       </c>
       <c r="F24">
-        <v>3.55206826881587</v>
+        <v>3.69039734140936</v>
       </c>
       <c r="G24">
-        <v>-6.686362945062979</v>
+        <v>-2.909907779322461</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.5393885542074038</v>
       </c>
       <c r="E25">
-        <v>-28.70160619154256</v>
+        <v>-29.06858466817615</v>
       </c>
       <c r="F25">
-        <v>3.179268146125175</v>
+        <v>3.491390356560807</v>
       </c>
       <c r="G25">
-        <v>-6.323904556150334</v>
+        <v>-3.884717776634098</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.3469057948971025</v>
       </c>
       <c r="E26">
-        <v>-29.40452045548716</v>
+        <v>-28.89702795886956</v>
       </c>
       <c r="F26">
-        <v>3.852041642922044</v>
+        <v>3.722670535422429</v>
       </c>
       <c r="G26">
-        <v>-6.209276916853069</v>
+        <v>-4.538163186812063</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1466479172635794</v>
       </c>
       <c r="E27">
-        <v>-28.68154505168858</v>
+        <v>-28.50140688413746</v>
       </c>
       <c r="F27">
-        <v>3.580186371936497</v>
+        <v>3.517444168113657</v>
       </c>
       <c r="G27">
-        <v>-6.182918353269391</v>
+        <v>-3.119183915587489</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.04985035447536282</v>
       </c>
       <c r="E28">
-        <v>-29.01036660633354</v>
+        <v>-29.04902618893702</v>
       </c>
       <c r="F28">
-        <v>3.962313911582714</v>
+        <v>3.850820629370318</v>
       </c>
       <c r="G28">
-        <v>-6.115873185008072</v>
+        <v>-4.165236852904242</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.229665224017074</v>
       </c>
       <c r="E29">
-        <v>-28.42898752780679</v>
+        <v>-29.70536962618674</v>
       </c>
       <c r="F29">
-        <v>3.594744100673295</v>
+        <v>3.800845223959423</v>
       </c>
       <c r="G29">
-        <v>-6.008601577899067</v>
+        <v>-4.067257947123972</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.3801815484466384</v>
       </c>
       <c r="E30">
-        <v>-28.60853699373692</v>
+        <v>-29.31732468846947</v>
       </c>
       <c r="F30">
-        <v>3.81224521615675</v>
+        <v>3.99865770301314</v>
       </c>
       <c r="G30">
-        <v>-5.91533357842118</v>
+        <v>-3.839909542760062</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.4870172840998597</v>
       </c>
       <c r="E31">
-        <v>-28.06775115621493</v>
+        <v>-27.6835101366641</v>
       </c>
       <c r="F31">
-        <v>3.630677021871932</v>
+        <v>3.853236148716881</v>
       </c>
       <c r="G31">
-        <v>-6.132541781798301</v>
+        <v>-4.018659138607471</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.5381532625718896</v>
       </c>
       <c r="E32">
-        <v>-28.16855951609968</v>
+        <v>-28.10803193251316</v>
       </c>
       <c r="F32">
-        <v>3.233330716301482</v>
+        <v>3.851791475966399</v>
       </c>
       <c r="G32">
-        <v>-5.70665334035322</v>
+        <v>-4.287177487297757</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5252323357333678</v>
       </c>
       <c r="E33">
-        <v>-28.51461191434382</v>
+        <v>-27.64303463598354</v>
       </c>
       <c r="F33">
-        <v>3.114710160955398</v>
+        <v>3.690180309149826</v>
       </c>
       <c r="G33">
-        <v>-5.701214114032198</v>
+        <v>-4.628769507676376</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.4409937598376514</v>
       </c>
       <c r="E34">
-        <v>-27.07100685628264</v>
+        <v>-28.11981955035512</v>
       </c>
       <c r="F34">
-        <v>3.568373852772576</v>
+        <v>3.467811706807522</v>
       </c>
       <c r="G34">
-        <v>-6.425041722375068</v>
+        <v>-5.350226765413128</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.2803386620249887</v>
       </c>
       <c r="E35">
-        <v>-26.13883406722572</v>
+        <v>-26.84000486867737</v>
       </c>
       <c r="F35">
-        <v>3.751979830868281</v>
+        <v>3.797841563756872</v>
       </c>
       <c r="G35">
-        <v>-7.458173600452046</v>
+        <v>-4.712026417443507</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.04373173053761335</v>
       </c>
       <c r="E36">
-        <v>-27.20560668921263</v>
+        <v>-26.10693549631569</v>
       </c>
       <c r="F36">
-        <v>3.75463392002685</v>
+        <v>3.830348357377531</v>
       </c>
       <c r="G36">
-        <v>-7.890120340233993</v>
+        <v>-5.269310411342262</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2619578370602854</v>
       </c>
       <c r="E37">
-        <v>-26.44353696930582</v>
+        <v>-25.87036348568098</v>
       </c>
       <c r="F37">
-        <v>3.835610147120113</v>
+        <v>4.244578447351841</v>
       </c>
       <c r="G37">
-        <v>-7.448854414758997</v>
+        <v>-5.591856863233453</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6291844706680577</v>
       </c>
       <c r="E38">
-        <v>-25.20516235327226</v>
+        <v>-24.69858460840421</v>
       </c>
       <c r="F38">
-        <v>4.337547777702834</v>
+        <v>4.116817686083267</v>
       </c>
       <c r="G38">
-        <v>-7.376257461628319</v>
+        <v>-5.082569158563052</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.044660160227552</v>
       </c>
       <c r="E39">
-        <v>-25.546840245625</v>
+        <v>-25.64800182648234</v>
       </c>
       <c r="F39">
-        <v>3.933047691241808</v>
+        <v>4.294027011094554</v>
       </c>
       <c r="G39">
-        <v>-6.605115536438185</v>
+        <v>-4.253449649343662</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.488243517083318</v>
       </c>
       <c r="E40">
-        <v>-23.86434006976317</v>
+        <v>-24.50474780697989</v>
       </c>
       <c r="F40">
-        <v>4.024933517029941</v>
+        <v>4.117026434668772</v>
       </c>
       <c r="G40">
-        <v>-7.685151223715557</v>
+        <v>-5.745317201706369</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.940694804969243</v>
       </c>
       <c r="E41">
-        <v>-24.31072986659526</v>
+        <v>-23.99065732373312</v>
       </c>
       <c r="F41">
-        <v>3.840106525382509</v>
+        <v>3.748737600853723</v>
       </c>
       <c r="G41">
-        <v>-7.357023192045154</v>
+        <v>-5.083310720763849</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.381539716204015</v>
       </c>
       <c r="E42">
-        <v>-22.07242743340201</v>
+        <v>-23.38556262682821</v>
       </c>
       <c r="F42">
-        <v>3.567465962099107</v>
+        <v>4.055487020314797</v>
       </c>
       <c r="G42">
-        <v>-7.578816500994166</v>
+        <v>-6.026753299090891</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.789472730976813</v>
       </c>
       <c r="E43">
-        <v>-22.87644893651587</v>
+        <v>-21.86302626681333</v>
       </c>
       <c r="F43">
-        <v>4.268886060419589</v>
+        <v>4.122473778709582</v>
       </c>
       <c r="G43">
-        <v>-8.38788734642773</v>
+        <v>-4.965812838484036</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.145849885593166</v>
       </c>
       <c r="E44">
-        <v>-21.65501987021901</v>
+        <v>-22.37915456336355</v>
       </c>
       <c r="F44">
-        <v>3.701416284601399</v>
+        <v>3.969351721036899</v>
       </c>
       <c r="G44">
-        <v>-7.753507368010428</v>
+        <v>-5.735796072735425</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.439978137180802</v>
       </c>
       <c r="E45">
-        <v>-21.26047657230072</v>
+        <v>-21.28759307465866</v>
       </c>
       <c r="F45">
-        <v>3.908421985091384</v>
+        <v>4.105896490244758</v>
       </c>
       <c r="G45">
-        <v>-8.001036857981735</v>
+        <v>-5.383504369173882</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.665526209723911</v>
       </c>
       <c r="E46">
-        <v>-22.28323242693308</v>
+        <v>-20.21771391950249</v>
       </c>
       <c r="F46">
-        <v>3.782960771732982</v>
+        <v>3.977267599938051</v>
       </c>
       <c r="G46">
-        <v>-7.64952313262192</v>
+        <v>-5.034500037332834</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.819095178060564</v>
       </c>
       <c r="E47">
-        <v>-21.55701916421901</v>
+        <v>-21.30166304340049</v>
       </c>
       <c r="F47">
-        <v>3.67862955408519</v>
+        <v>4.045097636348886</v>
       </c>
       <c r="G47">
-        <v>-7.415748959366285</v>
+        <v>-5.072210461570672</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.908156504439547</v>
       </c>
       <c r="E48">
-        <v>-20.01201251617807</v>
+        <v>-20.3156648122884</v>
       </c>
       <c r="F48">
-        <v>3.646878231535885</v>
+        <v>3.995208381147882</v>
       </c>
       <c r="G48">
-        <v>-7.439187621784325</v>
+        <v>-5.58646398454998</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.943711254624359</v>
       </c>
       <c r="E49">
-        <v>-19.83475898656984</v>
+        <v>-19.89096640595304</v>
       </c>
       <c r="F49">
-        <v>3.761863910718484</v>
+        <v>4.232890183298339</v>
       </c>
       <c r="G49">
-        <v>-7.771063191005183</v>
+        <v>-5.078225722815528</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.93690018872165</v>
       </c>
       <c r="E50">
-        <v>-19.54476003959264</v>
+        <v>-19.39997114014539</v>
       </c>
       <c r="F50">
-        <v>3.814415538752085</v>
+        <v>4.052998604636787</v>
       </c>
       <c r="G50">
-        <v>-8.756046494759</v>
+        <v>-5.153888241115571</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.90597754440548</v>
       </c>
       <c r="E51">
-        <v>-18.46482767213944</v>
+        <v>-19.01910383373027</v>
       </c>
       <c r="F51">
-        <v>3.593615864270682</v>
+        <v>4.114471749598539</v>
       </c>
       <c r="G51">
-        <v>-8.051595509457485</v>
+        <v>-5.73513727417311</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.870368687747581</v>
       </c>
       <c r="E52">
-        <v>-18.51526128716286</v>
+        <v>-18.09358790146463</v>
       </c>
       <c r="F52">
-        <v>3.460134397718376</v>
+        <v>3.983342846470182</v>
       </c>
       <c r="G52">
-        <v>-8.460818664657875</v>
+        <v>-5.51601226492875</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.845460807329626</v>
       </c>
       <c r="E53">
-        <v>-17.87786951363525</v>
+        <v>-18.25640465593641</v>
       </c>
       <c r="F53">
-        <v>3.615826051074543</v>
+        <v>4.165204282815592</v>
       </c>
       <c r="G53">
-        <v>-7.704709926761571</v>
+        <v>-4.554507350139445</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.845042165962789</v>
       </c>
       <c r="E54">
-        <v>-16.89702015746987</v>
+        <v>-16.77455663488045</v>
       </c>
       <c r="F54">
-        <v>3.668545009323509</v>
+        <v>4.101365320551445</v>
       </c>
       <c r="G54">
-        <v>-7.589675090362975</v>
+        <v>-5.635877187269142</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.884621199352846</v>
       </c>
       <c r="E55">
-        <v>-17.85491015041636</v>
+        <v>-17.31263444494585</v>
       </c>
       <c r="F55">
-        <v>3.45793425389654</v>
+        <v>4.117540022458508</v>
       </c>
       <c r="G55">
-        <v>-7.688173751792911</v>
+        <v>-5.764832867660372</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.972170564624524</v>
       </c>
       <c r="E56">
-        <v>-16.99114901819331</v>
+        <v>-16.46638945018447</v>
       </c>
       <c r="F56">
-        <v>3.453555503805342</v>
+        <v>4.118273955977388</v>
       </c>
       <c r="G56">
-        <v>-8.840521685284584</v>
+        <v>-5.987973568643868</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.105669679964898</v>
       </c>
       <c r="E57">
-        <v>-16.10117254993986</v>
+        <v>-15.53893080256954</v>
       </c>
       <c r="F57">
-        <v>3.41117954094773</v>
+        <v>3.763697916148282</v>
       </c>
       <c r="G57">
-        <v>-8.350686746202939</v>
+        <v>-5.707616709105149</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.290831293997539</v>
       </c>
       <c r="E58">
-        <v>-15.76089848452951</v>
+        <v>-14.46754819404282</v>
       </c>
       <c r="F58">
-        <v>3.495242264983824</v>
+        <v>3.632562386080704</v>
       </c>
       <c r="G58">
-        <v>-8.447748630868832</v>
+        <v>-5.897042814316706</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.524865549730247</v>
       </c>
       <c r="E59">
-        <v>-15.90730404919749</v>
+        <v>-14.55607986089278</v>
       </c>
       <c r="F59">
-        <v>3.401910109710404</v>
+        <v>4.061699775835794</v>
       </c>
       <c r="G59">
-        <v>-8.615848201716405</v>
+        <v>-6.587943736725985</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.795861447674174</v>
       </c>
       <c r="E60">
-        <v>-15.34281617871936</v>
+        <v>-14.56767728282642</v>
       </c>
       <c r="F60">
-        <v>3.865080145842108</v>
+        <v>4.209167397616967</v>
       </c>
       <c r="G60">
-        <v>-8.462417658153342</v>
+        <v>-6.07481910977557</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.098037679410649</v>
       </c>
       <c r="E61">
-        <v>-16.21459723840998</v>
+        <v>-14.30403405457386</v>
       </c>
       <c r="F61">
-        <v>3.334106581056459</v>
+        <v>3.777380888907725</v>
       </c>
       <c r="G61">
-        <v>-8.844616830116662</v>
+        <v>-7.0510195362137</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.424047999504507</v>
       </c>
       <c r="E62">
-        <v>-15.98058381558961</v>
+        <v>-13.7049939274172</v>
       </c>
       <c r="F62">
-        <v>3.026383001529693</v>
+        <v>4.0835686752697</v>
       </c>
       <c r="G62">
-        <v>-8.83712506556129</v>
+        <v>-6.818241837165385</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.760717775108591</v>
       </c>
       <c r="E63">
-        <v>-14.26440990700674</v>
+        <v>-15.47032442135333</v>
       </c>
       <c r="F63">
-        <v>3.080021447595767</v>
+        <v>4.199659396567634</v>
       </c>
       <c r="G63">
-        <v>-9.281112259469568</v>
+        <v>-7.240796559252421</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.094230020939754</v>
       </c>
       <c r="E64">
-        <v>-14.67094913257134</v>
+        <v>-13.46131674106446</v>
       </c>
       <c r="F64">
-        <v>3.146618873311235</v>
+        <v>3.407654009281416</v>
       </c>
       <c r="G64">
-        <v>-9.005069040768518</v>
+        <v>-7.869095065514082</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.419301046782237</v>
       </c>
       <c r="E65">
-        <v>-14.32942520833487</v>
+        <v>-13.48157713377478</v>
       </c>
       <c r="F65">
-        <v>3.025123883077438</v>
+        <v>3.910593964421524</v>
       </c>
       <c r="G65">
-        <v>-9.13619643903351</v>
+        <v>-7.350421964239847</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.726342005208187</v>
       </c>
       <c r="E66">
-        <v>-14.14580464427185</v>
+        <v>-13.1336182479734</v>
       </c>
       <c r="F66">
-        <v>2.967038760793136</v>
+        <v>3.496549428745442</v>
       </c>
       <c r="G66">
-        <v>-9.09477489324615</v>
+        <v>-7.055571536330198</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.999827442702631</v>
       </c>
       <c r="E67">
-        <v>-14.6218061326401</v>
+        <v>-14.29261777160052</v>
       </c>
       <c r="F67">
-        <v>3.203686760424899</v>
+        <v>3.303292970407123</v>
       </c>
       <c r="G67">
-        <v>-9.229924604341356</v>
+        <v>-7.343274496420561</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.238354354373373</v>
       </c>
       <c r="E68">
-        <v>-13.78426486492147</v>
+        <v>-13.49345079262289</v>
       </c>
       <c r="F68">
-        <v>3.22364544462795</v>
+        <v>3.497054732861149</v>
       </c>
       <c r="G68">
-        <v>-8.925188887451444</v>
+        <v>-7.232175898668158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.436929102066884</v>
       </c>
       <c r="E69">
-        <v>-14.61911169060554</v>
+        <v>-13.60607394119365</v>
       </c>
       <c r="F69">
-        <v>3.038463911732121</v>
+        <v>3.029052001301513</v>
       </c>
       <c r="G69">
-        <v>-8.024071633843983</v>
+        <v>-8.089080816598653</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.586105066101462</v>
       </c>
       <c r="E70">
-        <v>-14.94277078488176</v>
+        <v>-13.08783990422986</v>
       </c>
       <c r="F70">
-        <v>2.953933988480848</v>
+        <v>3.412811424731245</v>
       </c>
       <c r="G70">
-        <v>-8.789555836707503</v>
+        <v>-7.476120067820434</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.684466781590528</v>
       </c>
       <c r="E71">
-        <v>-14.40009204522456</v>
+        <v>-13.6397567308627</v>
       </c>
       <c r="F71">
-        <v>3.219291545558836</v>
+        <v>3.034366806557875</v>
       </c>
       <c r="G71">
-        <v>-8.447900915963638</v>
+        <v>-7.057190393098901</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.732931653463141</v>
       </c>
       <c r="E72">
-        <v>-13.38936381755659</v>
+        <v>-13.80318935779953</v>
       </c>
       <c r="F72">
-        <v>2.845929789769043</v>
+        <v>3.301081229441648</v>
       </c>
       <c r="G72">
-        <v>-8.190347094099419</v>
+        <v>-7.25292639810831</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.728290303297096</v>
       </c>
       <c r="E73">
-        <v>-14.88619203062992</v>
+        <v>-14.08537215863949</v>
       </c>
       <c r="F73">
-        <v>2.863946780779932</v>
+        <v>2.712148454216923</v>
       </c>
       <c r="G73">
-        <v>-8.028934825241173</v>
+        <v>-7.380379090824712</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.668311486396783</v>
       </c>
       <c r="E74">
-        <v>-15.23132967712452</v>
+        <v>-14.16253282725618</v>
       </c>
       <c r="F74">
-        <v>3.021185824444529</v>
+        <v>2.92973903337988</v>
       </c>
       <c r="G74">
-        <v>-8.523397906986718</v>
+        <v>-7.583543960024246</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.559748862382181</v>
       </c>
       <c r="E75">
-        <v>-15.20202139334688</v>
+        <v>-13.13681082214881</v>
       </c>
       <c r="F75">
-        <v>2.623276229040175</v>
+        <v>2.821072140745835</v>
       </c>
       <c r="G75">
-        <v>-7.68050321777842</v>
+        <v>-6.694758488550571</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.404699301036117</v>
       </c>
       <c r="E76">
-        <v>-15.90772066880619</v>
+        <v>-13.93787070326165</v>
       </c>
       <c r="F76">
-        <v>2.544354353105855</v>
+        <v>2.549937549400723</v>
       </c>
       <c r="G76">
-        <v>-7.634880589701724</v>
+        <v>-6.893358115451449</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.20022136581682</v>
       </c>
       <c r="E77">
-        <v>-15.19313652734383</v>
+        <v>-14.66980795712141</v>
       </c>
       <c r="F77">
-        <v>2.790917910549128</v>
+        <v>2.802162169674728</v>
       </c>
       <c r="G77">
-        <v>-7.596127343619015</v>
+        <v>-6.857432075259278</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.956219057981818</v>
       </c>
       <c r="E78">
-        <v>-16.08722937847025</v>
+        <v>-14.99694491943552</v>
       </c>
       <c r="F78">
-        <v>2.48020226796345</v>
+        <v>2.584641173373606</v>
       </c>
       <c r="G78">
-        <v>-7.215259010962483</v>
+        <v>-6.297565855839892</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.676128548252488</v>
       </c>
       <c r="E79">
-        <v>-17.48180464845039</v>
+        <v>-15.44469325846992</v>
       </c>
       <c r="F79">
-        <v>2.31995293715708</v>
+        <v>2.321581507470984</v>
       </c>
       <c r="G79">
-        <v>-6.500376496666723</v>
+        <v>-5.968557219056043</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.35900164799506</v>
       </c>
       <c r="E80">
-        <v>-18.06811070669748</v>
+        <v>-16.61226065491955</v>
       </c>
       <c r="F80">
-        <v>2.627215944407889</v>
+        <v>2.323256466359445</v>
       </c>
       <c r="G80">
-        <v>-7.011372442835389</v>
+        <v>-5.619149000659204</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.011455319776697</v>
       </c>
       <c r="E81">
-        <v>-17.86577848803476</v>
+        <v>-17.04905008685538</v>
       </c>
       <c r="F81">
-        <v>2.394370151154976</v>
+        <v>2.628480033064561</v>
       </c>
       <c r="G81">
-        <v>-6.513866969739253</v>
+        <v>-4.302975410611159</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.63994951054101</v>
       </c>
       <c r="E82">
-        <v>-18.66874485670483</v>
+        <v>-18.02212858162359</v>
       </c>
       <c r="F82">
-        <v>2.191995024446641</v>
+        <v>2.761610271838081</v>
       </c>
       <c r="G82">
-        <v>-5.953318777938778</v>
+        <v>-4.773437037196987</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.247110943298801</v>
       </c>
       <c r="E83">
-        <v>-19.90610056608667</v>
+        <v>-18.66011358524621</v>
       </c>
       <c r="F83">
-        <v>2.863764539951316</v>
+        <v>2.55237460629976</v>
       </c>
       <c r="G83">
-        <v>-5.168007717840563</v>
+        <v>-4.741983544028372</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.837204191138758</v>
       </c>
       <c r="E84">
-        <v>-20.65251082287495</v>
+        <v>-19.57553102047476</v>
       </c>
       <c r="F84">
-        <v>2.469410297439778</v>
+        <v>2.396644848043064</v>
       </c>
       <c r="G84">
-        <v>-4.939037146162411</v>
+        <v>-4.048540122644932</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.422254121075806</v>
       </c>
       <c r="E85">
-        <v>-21.66621878643997</v>
+        <v>-20.4427745492097</v>
       </c>
       <c r="F85">
-        <v>2.208872181911278</v>
+        <v>2.391797242001881</v>
       </c>
       <c r="G85">
-        <v>-4.187844568391925</v>
+        <v>-3.950306304858139</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.009173493718024</v>
       </c>
       <c r="E86">
-        <v>-22.62849234222588</v>
+        <v>-22.25895074930395</v>
       </c>
       <c r="F86">
-        <v>2.655143523025872</v>
+        <v>2.448263734381112</v>
       </c>
       <c r="G86">
-        <v>-4.516873068449009</v>
+        <v>-3.868602040948926</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.60159038569229</v>
       </c>
       <c r="E87">
-        <v>-23.96819156418107</v>
+        <v>-22.50307625458345</v>
       </c>
       <c r="F87">
-        <v>2.124214690079974</v>
+        <v>2.529818161921529</v>
       </c>
       <c r="G87">
-        <v>-4.450705194755597</v>
+        <v>-2.726943859003561</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.214799231162203</v>
       </c>
       <c r="E88">
-        <v>-25.71154084528397</v>
+        <v>-23.91414875537353</v>
       </c>
       <c r="F88">
-        <v>2.313905855116644</v>
+        <v>2.314046677575119</v>
       </c>
       <c r="G88">
-        <v>-4.079397717616479</v>
+        <v>-2.749902492318406</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.859427592605819</v>
       </c>
       <c r="E89">
-        <v>-26.23826577101214</v>
+        <v>-26.61158411125647</v>
       </c>
       <c r="F89">
-        <v>2.415307965628137</v>
+        <v>2.256244856942576</v>
       </c>
       <c r="G89">
-        <v>-3.886194279944613</v>
+        <v>-2.892252639961528</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.543551645546653</v>
       </c>
       <c r="E90">
-        <v>-28.27684438657109</v>
+        <v>-26.58921797813258</v>
       </c>
       <c r="F90">
-        <v>2.025585953633053</v>
+        <v>2.189554654077993</v>
       </c>
       <c r="G90">
-        <v>-3.210326544829164</v>
+        <v>-1.715459638207878</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.279950514007994</v>
       </c>
       <c r="E91">
-        <v>-29.71907052429695</v>
+        <v>-28.47111592150015</v>
       </c>
       <c r="F91">
-        <v>1.834393786862511</v>
+        <v>1.655940254012219</v>
       </c>
       <c r="G91">
-        <v>-3.44019096380292</v>
+        <v>-2.267069357052321</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.084253345715258</v>
       </c>
       <c r="E92">
-        <v>-31.53551164012065</v>
+        <v>-31.35773733600153</v>
       </c>
       <c r="F92">
-        <v>1.701876539967063</v>
+        <v>2.082163447244259</v>
       </c>
       <c r="G92">
-        <v>-3.482622225979759</v>
+        <v>-1.510732191513808</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.967294477558931</v>
       </c>
       <c r="E93">
-        <v>-33.17248027407235</v>
+        <v>-32.61183481378973</v>
       </c>
       <c r="F93">
-        <v>1.810525208518246</v>
+        <v>1.623547775093147</v>
       </c>
       <c r="G93">
-        <v>-3.506196620764909</v>
+        <v>-2.477378383525602</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.934676624591733</v>
       </c>
       <c r="E94">
-        <v>-35.75430368853946</v>
+        <v>-35.53976949666308</v>
       </c>
       <c r="F94">
-        <v>1.956122376703898</v>
+        <v>1.251706901854894</v>
       </c>
       <c r="G94">
-        <v>-3.489213522148447</v>
+        <v>-2.296834471995909</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.998184642581716</v>
       </c>
       <c r="E95">
-        <v>-37.52833111680732</v>
+        <v>-36.8342020924376</v>
       </c>
       <c r="F95">
-        <v>1.422324079074702</v>
+        <v>1.000968372701511</v>
       </c>
       <c r="G95">
-        <v>-3.158748245327319</v>
+        <v>-1.934928944188322</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.166559066514106</v>
       </c>
       <c r="E96">
-        <v>-40.32660653189306</v>
+        <v>-39.15040107127379</v>
       </c>
       <c r="F96">
-        <v>1.037537480065498</v>
+        <v>1.22105068101209</v>
       </c>
       <c r="G96">
-        <v>-3.439634792152322</v>
+        <v>-2.84445829401107</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.428607020848276</v>
       </c>
       <c r="E97">
-        <v>-41.85695450957117</v>
+        <v>-41.37051941708924</v>
       </c>
       <c r="F97">
-        <v>1.492698860146937</v>
+        <v>0.6341606598026678</v>
       </c>
       <c r="G97">
-        <v>-4.330919725508147</v>
+        <v>-1.650615982730173</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.796412531706851</v>
       </c>
       <c r="E98">
-        <v>-44.76317742381475</v>
+        <v>-43.18636277434393</v>
       </c>
       <c r="F98">
-        <v>1.164438395969966</v>
+        <v>0.6449625707351733</v>
       </c>
       <c r="G98">
-        <v>-3.809863031445637</v>
+        <v>-3.595895852151461</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.242682837802639</v>
       </c>
       <c r="E99">
-        <v>-46.01602957125083</v>
+        <v>-46.5864995558931</v>
       </c>
       <c r="F99">
-        <v>0.9572620517950038</v>
+        <v>0.2610830340320348</v>
       </c>
       <c r="G99">
-        <v>-4.511069682118667</v>
+        <v>-3.264116288751242</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.786589001080655</v>
       </c>
       <c r="E100">
-        <v>-49.13614816253571</v>
+        <v>-48.97025657421273</v>
       </c>
       <c r="F100">
-        <v>0.4176693241832254</v>
+        <v>0.2392845458273658</v>
       </c>
       <c r="G100">
-        <v>-4.504100983758502</v>
+        <v>-3.902187525444832</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.357493841236569</v>
       </c>
       <c r="E101">
-        <v>-50.58731916854521</v>
+        <v>-49.88332599566829</v>
       </c>
       <c r="F101">
-        <v>0.008048270438092245</v>
+        <v>-0.1710406202101469</v>
       </c>
       <c r="G101">
-        <v>-4.473240078241416</v>
+        <v>-3.297758052521316</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.030387642077818</v>
       </c>
       <c r="E102">
-        <v>-52.66016135056471</v>
+        <v>-53.23973243584389</v>
       </c>
       <c r="F102">
-        <v>0.06845696328724619</v>
+        <v>-0.2986771263683003</v>
       </c>
       <c r="G102">
-        <v>-5.39672999860327</v>
+        <v>-3.730846930514312</v>
       </c>
     </row>
   </sheetData>
